--- a/Data/Mount Ownership - 3741896357/1.6/Mount Ownership - 3741896357.xlsx
+++ b/Data/Mount Ownership - 3741896357/1.6/Mount Ownership - 3741896357.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zilrt\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\알티\갱신\Mount Ownership - 3741896357\1.6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4319E029-788D-4DF2-A103-C9D51A139AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF4A6E2-CC11-4575-8318-1EC2BDFC604D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="543">
   <si>
     <t>Class+Node [(Identifier (Key)]</t>
   </si>
@@ -52,6 +52,9 @@
     <t>mount ownership</t>
   </si>
   <si>
+    <t>탈것 소유권</t>
+  </si>
+  <si>
     <t>PreceptDef+CompanionMounts_PersonalMountsDesired.label</t>
   </si>
   <si>
@@ -64,6 +67,9 @@
     <t>Important</t>
   </si>
   <si>
+    <t>중요함</t>
+  </si>
+  <si>
     <t>PreceptDef+CompanionMounts_PersonalMountsDesired.description</t>
   </si>
   <si>
@@ -73,6 +79,9 @@
     <t>Followers believe that capable people should keep personal mounts.</t>
   </si>
   <si>
+    <t>추종자들은 능력 있는 사람이라면 개인 탈것을 보유해야 한다고 믿습니다.</t>
+  </si>
+  <si>
     <t>PreceptDef+CompanionMounts_PersonalMountsEssential.label</t>
   </si>
   <si>
@@ -82,6 +91,9 @@
     <t>Essential</t>
   </si>
   <si>
+    <t>필수</t>
+  </si>
+  <si>
     <t>PreceptDef+CompanionMounts_PersonalMountsEssential.description</t>
   </si>
   <si>
@@ -91,6 +103,9 @@
     <t>Followers believe that every capable person must keep a personal mount.</t>
   </si>
   <si>
+    <t>추종자들은 능력 있는 사람이라면 누구나 반드시 개인 탈것을 보유해야 한다고 믿습니다.</t>
+  </si>
+  <si>
     <t>ThoughtDef+CompanionMounts_PersonalMountExpectation.stages.0.label</t>
   </si>
   <si>
@@ -103,6 +118,9 @@
     <t>no personal mount</t>
   </si>
   <si>
+    <t>개인 탈것 없음</t>
+  </si>
+  <si>
     <t>ThoughtDef+CompanionMounts_PersonalMountExpectation.stages.0.description</t>
   </si>
   <si>
@@ -112,6 +130,9 @@
     <t>Having to walk everywhere kind of gets old.</t>
   </si>
   <si>
+    <t>어디든 걸어 다녀야 하니 지긋지긋해.</t>
+  </si>
+  <si>
     <t>ThoughtDef+CompanionMounts_PersonalMountExpectation.stages.1.label</t>
   </si>
   <si>
@@ -121,6 +142,9 @@
     <t>has personal mount</t>
   </si>
   <si>
+    <t>개인 탈것 보유</t>
+  </si>
+  <si>
     <t>ThoughtDef+CompanionMounts_PersonalMountExpectation.stages.1.description</t>
   </si>
   <si>
@@ -130,6 +154,9 @@
     <t>I am glad that I have a personal mount.</t>
   </si>
   <si>
+    <t>나만의 탈것이 있어서 기뻐.</t>
+  </si>
+  <si>
     <t>ThoughtDef+CompanionMounts_PersonalMountExpectation.stages.2.label</t>
   </si>
   <si>
@@ -139,6 +166,9 @@
     <t>has several personal mounts</t>
   </si>
   <si>
+    <t>개인 탈것 여러 마리 보유</t>
+  </si>
+  <si>
     <t>ThoughtDef+CompanionMounts_PersonalMountExpectation.stages.2.description</t>
   </si>
   <si>
@@ -163,6 +193,9 @@
     <t>Life requires a personal mount, but I don't have one. Will I get one soon?</t>
   </si>
   <si>
+    <t>살아가려면 탈것이 필요한데, 나는 없네. 금방 하나를 얻을 수 있겠지?</t>
+  </si>
+  <si>
     <t>ThoughtDef+CompanionMounts_PersonalMountExpectation.stages.4.label</t>
   </si>
   <si>
@@ -178,6 +211,9 @@
     <t>I own a mount of my very own!</t>
   </si>
   <si>
+    <t>나만의 탈것이 생겼어!</t>
+  </si>
+  <si>
     <t>ThoughtDef+CompanionMounts_PersonalMountExpectation.stages.5.label</t>
   </si>
   <si>
@@ -193,6 +229,9 @@
     <t>I own several mounts, life is good!</t>
   </si>
   <si>
+    <t>나는 탈것이 여러 마리야. 삶이 만족스러워!</t>
+  </si>
+  <si>
     <t>JoyKindDef+CompanionMounts_Joyriding.label</t>
   </si>
   <si>
@@ -205,6 +244,9 @@
     <t>joyriding</t>
   </si>
   <si>
+    <t>승마 유람</t>
+  </si>
+  <si>
     <t>JobDef+CompanionMounts_RideOwnedMountForLeisure.reportString</t>
   </si>
   <si>
@@ -217,6 +259,9 @@
     <t>riding TargetA for leisure.</t>
   </si>
   <si>
+    <t>TargetA을(를) 타고 여가를 즐기는 중.</t>
+  </si>
+  <si>
     <t>ThoughtDef+CompanionMounts_RidingOwnedMount.stages.0.label</t>
   </si>
   <si>
@@ -226,6 +271,9 @@
     <t>riding trusted mount</t>
   </si>
   <si>
+    <t>신뢰하는 탈것에 탑승</t>
+  </si>
+  <si>
     <t>ThoughtDef+CompanionMounts_RidingOwnedMount.stages.0.description</t>
   </si>
   <si>
@@ -235,6 +283,9 @@
     <t>Riding a mount I have started to trust feels reassuring.</t>
   </si>
   <si>
+    <t>신뢰가 쌓이기 시작한 탈것을 타니 마음이 놓여.</t>
+  </si>
+  <si>
     <t>ThoughtDef+CompanionMounts_RidingNamedMount.stages.0.label</t>
   </si>
   <si>
@@ -250,6 +301,9 @@
     <t>Riding a mount I deeply trust feels natural and comforting.</t>
   </si>
   <si>
+    <t>깊이 신뢰하는 탈것을 타니 자연스럽고 편안해.</t>
+  </si>
+  <si>
     <t>ThoughtDef+CompanionMounts_TrustedMountDied.stages.0.label</t>
   </si>
   <si>
@@ -259,6 +313,9 @@
     <t>trusted mount {0} died</t>
   </si>
   <si>
+    <t>신뢰하던 탈것 {0} 사망</t>
+  </si>
+  <si>
     <t>ThoughtDef+CompanionMounts_TrustedMountDied.stages.0.description</t>
   </si>
   <si>
@@ -268,6 +325,9 @@
     <t>My trusted mount {0} died. We had built a bond through work, travel, and danger, and losing them hurts.</t>
   </si>
   <si>
+    <t>내가 신뢰하던 탈것 {0}(이)가 죽었어. 함께 일하고 여행하며 위험을 헤쳐 나가는 동안 유대가 쌓였기에, 잃고 나니 마음이 아프다.</t>
+  </si>
+  <si>
     <t>ThoughtDef+CompanionMounts_TrustedMountDied.stages.1.label</t>
   </si>
   <si>
@@ -385,6 +445,9 @@
     <t>former trusted mount {0} died</t>
   </si>
   <si>
+    <t>이전에 신뢰하던 탈것 {0} 사망</t>
+  </si>
+  <si>
     <t>ThoughtDef+CompanionMounts_FormerTrustedMountDied.stages.0.description</t>
   </si>
   <si>
@@ -394,6 +457,9 @@
     <t>My former trusted mount {0} died. We were no longer paired, but I still remember the bond we shared.</t>
   </si>
   <si>
+    <t>이전에 신뢰하던 탈것 {0}(이)가 죽었어. 더는 짝을 이루고 있지 않았지만, 함께 나누었던 유대는 여전히 기억하고 있어.</t>
+  </si>
+  <si>
     <t>ThoughtDef+CompanionMounts_FormerTrustedMountDied.stages.1.label</t>
   </si>
   <si>
@@ -514,6 +580,9 @@
     <t>Mount owner</t>
   </si>
   <si>
+    <t>탈것 소유자</t>
+  </si>
+  <si>
     <t>RimHUD.CustomValueDef+CompanionMounts_MountOwner.description</t>
   </si>
   <si>
@@ -523,6 +592,9 @@
     <t>Shows the current Mount Ownership owner for an animal.</t>
   </si>
   <si>
+    <t>동물의 현재 탈것 소유자를 표시합니다.</t>
+  </si>
+  <si>
     <t>RimHUD.CustomBarDef+CompanionMounts_MountTrust.label</t>
   </si>
   <si>
@@ -535,6 +607,9 @@
     <t>Mount trust</t>
   </si>
   <si>
+    <t>탈것 신뢰도</t>
+  </si>
+  <si>
     <t>RimHUD.CustomBarDef+CompanionMounts_MountTrust.description</t>
   </si>
   <si>
@@ -544,6 +619,9 @@
     <t>Legacy Mount Ownership trust bar. Kept for compatibility with old RimHUD layouts; current layouts use the trust value row instead.</t>
   </si>
   <si>
+    <t>이전 방식의 탈것 소유권 신뢰도 막대입니다. 구형 RimHUD 레이아웃과의 호환성을 위해 유지되며, 현재 레이아웃에서는 대신 신뢰도 값 행을 사용합니다.</t>
+  </si>
+  <si>
     <t>RimHUD.CustomValueDef+CompanionMounts_MountTrustValue.label</t>
   </si>
   <si>
@@ -559,6 +637,9 @@
     <t>Shows Mount Ownership trust level and progress for animals with trust level 1 or higher, or level 0 animals that are at least 10% toward level 1.</t>
   </si>
   <si>
+    <t>신뢰도 레벨이 1 이상인 동물과, 레벨 1까지 진행도가 10% 이상인 레벨 0 동물의 탈것 신뢰도 레벨 및 진행도를 표시합니다.</t>
+  </si>
+  <si>
     <t>RimHUD.CustomValueDef+CompanionMounts_MountTrustEffects.label</t>
   </si>
   <si>
@@ -568,6 +649,9 @@
     <t>Mount trust effects</t>
   </si>
   <si>
+    <t>탈것 신뢰 효과</t>
+  </si>
+  <si>
     <t>RimHUD.CustomValueDef+CompanionMounts_MountTrustEffects.description</t>
   </si>
   <si>
@@ -577,6 +661,9 @@
     <t>Shows active Mount Ownership trust effects for an animal.</t>
   </si>
   <si>
+    <t>동물에게 적용 중인 탈것 신뢰 효과를 표시합니다.</t>
+  </si>
+  <si>
     <t>RimHUD.CustomValueDef+CompanionMounts_MountPreviousOwner.label</t>
   </si>
   <si>
@@ -586,6 +673,9 @@
     <t>Previous mount owner</t>
   </si>
   <si>
+    <t>이전 탈것 소유자</t>
+  </si>
+  <si>
     <t>RimHUD.CustomValueDef+CompanionMounts_MountPreviousOwner.description</t>
   </si>
   <si>
@@ -595,6 +685,9 @@
     <t>Shows the previous Mount Ownership owner for an animal.</t>
   </si>
   <si>
+    <t>동물의 이전 탈것 소유자를 표시합니다.</t>
+  </si>
+  <si>
     <t>PawnColumnDef+CompanionMountRider.label</t>
   </si>
   <si>
@@ -607,6 +700,9 @@
     <t>Owner</t>
   </si>
   <si>
+    <t>소유자</t>
+  </si>
+  <si>
     <t>PawnColumnDef+CompanionMountBorrow.label</t>
   </si>
   <si>
@@ -616,6 +712,9 @@
     <t>Borrow</t>
   </si>
   <si>
+    <t>빌리기</t>
+  </si>
+  <si>
     <t>PawnColumnDef+CompanionMounts_PreferredMate.label</t>
   </si>
   <si>
@@ -625,6 +724,9 @@
     <t>Mate</t>
   </si>
   <si>
+    <t>짝</t>
+  </si>
+  <si>
     <t>Keyed+CompanionMounts_RimHUD_Label_Owner</t>
   </si>
   <si>
@@ -643,6 +745,9 @@
     <t>Current mount owner: {0}</t>
   </si>
   <si>
+    <t>현재 탈것 소유자: {0}</t>
+  </si>
+  <si>
     <t>Keyed+CompanionMounts_RimHUD_Label_Trust</t>
   </si>
   <si>
@@ -652,6 +757,9 @@
     <t>Trust</t>
   </si>
   <si>
+    <t>신뢰도</t>
+  </si>
+  <si>
     <t>Keyed+CompanionMounts_RimHUD_Value_TrustLevel</t>
   </si>
   <si>
@@ -659,6 +767,9 @@
   </si>
   <si>
     <t>Level {0} ({1}%)</t>
+  </si>
+  <si>
+    <t>레벨 {0} ({1}%)</t>
   </si>
   <si>
     <t>Keyed+CompanionMounts_RimHUD_Tooltip_Trust</t>
@@ -672,256 +783,983 @@
 Trust XP: {2} / {3}</t>
   </si>
   <si>
-    <t>Keyed+CompanionMounts_RimHUD_Label_Effects</t>
-  </si>
-  <si>
-    <t>CompanionMounts_RimHUD_Label_Effects</t>
-  </si>
-  <si>
-    <t>Effects</t>
-  </si>
-  <si>
-    <t>Keyed+CompanionMounts_RimHUD_Tooltip_Effects</t>
-  </si>
-  <si>
-    <t>CompanionMounts_RimHUD_Tooltip_Effects</t>
-  </si>
-  <si>
-    <t>Current Mount Ownership trust effects: {0}</t>
-  </si>
-  <si>
-    <t>Keyed+CompanionMounts_TrustEffect_MoveSpeed</t>
-  </si>
-  <si>
-    <t>CompanionMounts_TrustEffect_MoveSpeed</t>
-  </si>
-  <si>
-    <t>+{0} c/s mounted</t>
-  </si>
-  <si>
-    <t>Keyed+CompanionMounts_TrustEffect_FasterMounting</t>
-  </si>
-  <si>
-    <t>CompanionMounts_TrustEffect_FasterMounting</t>
-  </si>
-  <si>
-    <t>{0}% faster mounting</t>
-  </si>
-  <si>
-    <t>Keyed+CompanionMounts_RimHUD_Label_Previous</t>
-  </si>
-  <si>
-    <t>CompanionMounts_RimHUD_Label_Previous</t>
-  </si>
-  <si>
-    <t>Previous</t>
-  </si>
-  <si>
-    <t>Keyed+CompanionMounts_RimHUD_Tooltip_Previous</t>
-  </si>
-  <si>
-    <t>CompanionMounts_RimHUD_Tooltip_Previous</t>
-  </si>
-  <si>
-    <t>Previous mount owner: {0}</t>
-  </si>
-  <si>
-    <t>Keyed+CompanionMounts_Inspect_Label_PreviousOwner</t>
-  </si>
-  <si>
-    <t>CompanionMounts_Inspect_Label_PreviousOwner</t>
-  </si>
-  <si>
-    <t>Previous Owner</t>
-  </si>
-  <si>
-    <t>Keyed+CompanionMounts_Inspect_TrustBarLabel</t>
-  </si>
-  <si>
-    <t>CompanionMounts_Inspect_TrustBarLabel</t>
-  </si>
-  <si>
-    <t>Trust: {0}</t>
-  </si>
-  <si>
-    <t>Keyed+CompanionMounts_Inspect_TrustTooltip</t>
-  </si>
-  <si>
-    <t>CompanionMounts_Inspect_TrustTooltip</t>
-  </si>
-  <si>
-    <t>Trust level: {0}
-Trust XP: {1} / {2}</t>
-  </si>
-  <si>
-    <t>Keyed+CompanionMounts_Inspect_TrustLevelProgress</t>
-  </si>
-  <si>
-    <t>CompanionMounts_Inspect_TrustLevelProgress</t>
-  </si>
-  <si>
-    <t>Trust: Level {0} ({1}%)</t>
-  </si>
-  <si>
-    <t>수정 전 기존 번역</t>
-  </si>
-  <si>
-    <t>탈것 소유권</t>
-  </si>
-  <si>
-    <t>중요함</t>
-  </si>
-  <si>
-    <t>추종자들은 능력 있는 사람이라면 개인 탈것을 보유해야 한다고 믿습니다.</t>
-  </si>
-  <si>
-    <t>필수</t>
-  </si>
-  <si>
-    <t>추종자들은 능력 있는 사람이라면 누구나 반드시 개인 탈것을 보유해야 한다고 믿습니다.</t>
-  </si>
-  <si>
-    <t>개인 탈것 없음</t>
-  </si>
-  <si>
-    <t>개인 탈것 보유</t>
-  </si>
-  <si>
-    <t>개인 탈것 여러 마리 보유</t>
-  </si>
-  <si>
-    <t>승마 유람</t>
-  </si>
-  <si>
-    <t>TargetA을(를) 타고 여가를 즐기는 중.</t>
-  </si>
-  <si>
-    <t>신뢰하는 탈것에 탑승</t>
-  </si>
-  <si>
-    <t>신뢰하던 탈것 {0} 사망</t>
-  </si>
-  <si>
-    <t>이전에 신뢰하던 탈것 {0} 사망</t>
-  </si>
-  <si>
-    <t>탈것 소유자</t>
-  </si>
-  <si>
-    <t>동물의 현재 탈것 소유자를 표시합니다.</t>
-  </si>
-  <si>
-    <t>탈것 신뢰도</t>
-  </si>
-  <si>
-    <t>이전 방식의 탈것 소유권 신뢰도 막대입니다. 구형 RimHUD 레이아웃과의 호환성을 위해 유지되며, 현재 레이아웃에서는 대신 신뢰도 값 행을 사용합니다.</t>
-  </si>
-  <si>
-    <t>신뢰도 레벨이 1 이상인 동물과, 레벨 1까지 진행도가 10% 이상인 레벨 0 동물의 탈것 신뢰도 레벨 및 진행도를 표시합니다.</t>
-  </si>
-  <si>
-    <t>탈것 신뢰 효과</t>
-  </si>
-  <si>
-    <t>동물에게 적용 중인 탈것 신뢰 효과를 표시합니다.</t>
-  </si>
-  <si>
-    <t>이전 탈것 소유자</t>
-  </si>
-  <si>
-    <t>동물의 이전 탈것 소유자를 표시합니다.</t>
-  </si>
-  <si>
-    <t>소유자</t>
-  </si>
-  <si>
-    <t>빌리기</t>
-  </si>
-  <si>
-    <t>짝</t>
-  </si>
-  <si>
-    <t>현재 탈것 소유자: {0}</t>
-  </si>
-  <si>
-    <t>신뢰도</t>
-  </si>
-  <si>
-    <t>레벨 {0} ({1}%)</t>
-  </si>
-  <si>
     <t>소유자: {0}
 신뢰도 레벨: {1}
 신뢰도 경험치: {2} / {3}</t>
   </si>
   <si>
+    <t>Keyed+CompanionMounts_RimHUD_Label_Effects</t>
+  </si>
+  <si>
+    <t>CompanionMounts_RimHUD_Label_Effects</t>
+  </si>
+  <si>
+    <t>Effects</t>
+  </si>
+  <si>
     <t>효과</t>
   </si>
   <si>
+    <t>Keyed+CompanionMounts_RimHUD_Tooltip_Effects</t>
+  </si>
+  <si>
+    <t>CompanionMounts_RimHUD_Tooltip_Effects</t>
+  </si>
+  <si>
+    <t>Current Mount Ownership trust effects: {0}</t>
+  </si>
+  <si>
     <t>현재 탈것 신뢰 효과: {0}</t>
   </si>
   <si>
+    <t>Keyed+CompanionMounts_TrustEffect_MoveSpeed</t>
+  </si>
+  <si>
+    <t>CompanionMounts_TrustEffect_MoveSpeed</t>
+  </si>
+  <si>
+    <t>+{0} c/s mounted</t>
+  </si>
+  <si>
     <t>탑승 시 이동 속도 +{0}칸/초</t>
   </si>
   <si>
+    <t>Keyed+CompanionMounts_TrustEffect_FasterMounting</t>
+  </si>
+  <si>
+    <t>CompanionMounts_TrustEffect_FasterMounting</t>
+  </si>
+  <si>
+    <t>{0}% faster mounting</t>
+  </si>
+  <si>
     <t>탑승 속도 {0}% 증가</t>
   </si>
   <si>
+    <t>Keyed+CompanionMounts_RimHUD_Label_Previous</t>
+  </si>
+  <si>
+    <t>CompanionMounts_RimHUD_Label_Previous</t>
+  </si>
+  <si>
+    <t>Previous</t>
+  </si>
+  <si>
     <t>이전</t>
   </si>
   <si>
+    <t>Keyed+CompanionMounts_RimHUD_Tooltip_Previous</t>
+  </si>
+  <si>
+    <t>CompanionMounts_RimHUD_Tooltip_Previous</t>
+  </si>
+  <si>
+    <t>Previous mount owner: {0}</t>
+  </si>
+  <si>
     <t>이전 탈것 소유자: {0}</t>
   </si>
   <si>
+    <t>Keyed+CompanionMounts_Inspect_Label_PreviousOwner</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Inspect_Label_PreviousOwner</t>
+  </si>
+  <si>
+    <t>Previous Owner</t>
+  </si>
+  <si>
     <t>이전 소유자</t>
   </si>
   <si>
+    <t>Keyed+CompanionMounts_RimHUD_Label_FormerOwner</t>
+  </si>
+  <si>
+    <t>CompanionMounts_RimHUD_Label_FormerOwner</t>
+  </si>
+  <si>
+    <t>Former Owner</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Inspect_TrustBarLabel</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Inspect_TrustBarLabel</t>
+  </si>
+  <si>
+    <t>Trust: {0}</t>
+  </si>
+  <si>
     <t>신뢰도: {0}</t>
   </si>
   <si>
-    <t>신뢰도: 레벨 {0} ({1}%)</t>
-  </si>
-  <si>
-    <t>어디든 걸어 다녀야 하니 지긋지긋해.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>나만의 탈것이 있어서 기뻐.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>탈것을 여러 마리라서 기분이 좋아.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>살아가려면 탈것이 필요한데, 나는 없네. 금방 하나를 얻을 수 있겠지?</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>나만의 탈것이 생겼어!</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>나는 탈것이 여러 마리야. 삶이 만족스러워!</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>신뢰가 쌓이기 시작한 탈것을 타니 마음이 놓여.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>깊이 신뢰하는 탈것을 타니 자연스럽고 편안해.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>내가 신뢰하던 탈것 {0}(이)가 죽었어. 함께 일하고 여행하며 위험을 헤쳐 나가는 동안 유대가 쌓였기에, 잃고 나니 마음이 아프다.</t>
-  </si>
-  <si>
-    <t>이전에 신뢰하던 탈것 {0}(이)가 죽었어. 더는 짝을 이루고 있지 않았지만, 함께 나누었던 유대는 여전히 기억하고 있어.</t>
+    <t>Keyed+CompanionMounts_Inspect_TrustTooltip</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Inspect_TrustTooltip</t>
+  </si>
+  <si>
+    <t>Trust level: {0}
+Trust XP: {1} / {2}</t>
   </si>
   <si>
     <t>신뢰도 레벨: {0}
 신뢰도 경험치: {1} / {2}</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Inspect_TrustLevelProgress</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Inspect_TrustLevelProgress</t>
+  </si>
+  <si>
+    <t>Trust: Level {0} ({1}%)</t>
+  </si>
+  <si>
+    <t>신뢰도: 레벨 {0} ({1}%)</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_StatPart_MountTrustMoveSpeed</t>
+  </si>
+  <si>
+    <t>CompanionMounts_StatPart_MountTrustMoveSpeed</t>
+  </si>
+  <si>
+    <t>Mount trust: +{0} c/s</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_SettingsCategory</t>
+  </si>
+  <si>
+    <t>CompanionMounts_SettingsCategory</t>
+  </si>
+  <si>
+    <t>Mount Ownership</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Common_None</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Common_None</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Common_Off</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Common_Off</t>
+  </si>
+  <si>
+    <t>Off</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Common_Reset</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Common_Reset</t>
+  </si>
+  <si>
+    <t>Reset</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_UsePreferredMateSystem</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_UsePreferredMateSystem</t>
+  </si>
+  <si>
+    <t>Use preferred stallion assignments</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_UsePreferredMateSystem_Tip</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_UsePreferredMateSystem_Tip</t>
+  </si>
+  <si>
+    <t>When enabled, female animals can be assigned a preferred stallion. Assigned mares mate exclusively with their assigned stallion, while unassigned animals keep vanilla mating behavior.</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_PreferredMateEnabledMessage</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_PreferredMateEnabledMessage</t>
+  </si>
+  <si>
+    <t>Preferred stallion assignments enabled. The Stallion column has been added to supported animal tabs.</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_PreferredMateDisabledMessage</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_PreferredMateDisabledMessage</t>
+  </si>
+  <si>
+    <t>Preferred stallion assignments disabled. The Stallion column has been removed from supported animal tabs.</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_AssignedMountAutoMountDistance</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_AssignedMountAutoMountDistance</t>
+  </si>
+  <si>
+    <t>Assigned mount minimum travel distance: {0} cells</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_AssignedMountMaxPickupDistance</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_AssignedMountMaxPickupDistance</t>
+  </si>
+  <si>
+    <t>Assigned mount maximum pickup distance: {0} cells</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_UseTrustSystem</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_UseTrustSystem</t>
+  </si>
+  <si>
+    <t>Use mount trust system</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_UseTrustSystem_Tip</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_UseTrustSystem_Tip</t>
+  </si>
+  <si>
+    <t>When disabled, mount trust XP, trust bonuses, trust mood thoughts, death memories, and trust HUD display are inactive. Existing trust progress is kept.</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_TrustXpForLevel10</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_TrustXpForLevel10</t>
+  </si>
+  <si>
+    <t>Trust XP for level 10: {0}</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_TrustCurve</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_TrustCurve</t>
+  </si>
+  <si>
+    <t>Trust curve: {0}</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_TrustMountedTravelXpPerTick</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_TrustMountedTravelXpPerTick</t>
+  </si>
+  <si>
+    <t>Mounted travel trust XP per tick: {0}</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_TrustLeisureRideMultiplier</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_TrustLeisureRideMultiplier</t>
+  </si>
+  <si>
+    <t>Leisure ride trust multiplier: {0}x</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_TrustFeedDownedMountXp</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_TrustFeedDownedMountXp</t>
+  </si>
+  <si>
+    <t>Feed downed mount trust XP: {0}</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_TrustRescueMountXp</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_TrustRescueMountXp</t>
+  </si>
+  <si>
+    <t>Rescue mount trust XP: {0}</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_TrustRescueMountMultiplier</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_TrustRescueMountMultiplier</t>
+  </si>
+  <si>
+    <t>Rescue trust multiplier: {0}x</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_TrustWildnessSlowdownStrength</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_TrustWildnessSlowdownStrength</t>
+  </si>
+  <si>
+    <t>Wildness XP slowdown strength: {0}</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_TrustMaxMountingTimeReduction</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_TrustMaxMountingTimeReduction</t>
+  </si>
+  <si>
+    <t>Trust mounting time reduction at level 10: {0}%</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_TrustMoveSpeedBonusLevel4</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_TrustMoveSpeedBonusLevel4</t>
+  </si>
+  <si>
+    <t>Trust MoveSpeed bonus at level 4: +{0} c/s</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_TrustMoveSpeedBonusLevel8</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_TrustMoveSpeedBonusLevel8</t>
+  </si>
+  <si>
+    <t>Trust MoveSpeed bonus at level 8: +{0} c/s</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_TrustMoveSpeedBonusLevel10</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_TrustMoveSpeedBonusLevel10</t>
+  </si>
+  <si>
+    <t>Trust MoveSpeed bonus at level 10: +{0} c/s</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_AutoInjectRimHudRows</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_AutoInjectRimHudRows</t>
+  </si>
+  <si>
+    <t>Automatically add Mount Ownership rows to RimHUD</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_AutoInjectRimHudRows_Tip</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_AutoInjectRimHudRows_Tip</t>
+  </si>
+  <si>
+    <t>When disabled, Mount Ownership's RimHUD values remain available for manual placement and will not be forced into another mod's preferred HUD location.</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_MountNamePools</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_MountNamePools</t>
+  </si>
+  <si>
+    <t>Mount name pools</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_NamePoolSimple</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_NamePoolSimple</t>
+  </si>
+  <si>
+    <t>Simple names</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_NamePoolMedieval</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_NamePoolMedieval</t>
+  </si>
+  <si>
+    <t>Medieval names</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_NamePoolRoman</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_NamePoolRoman</t>
+  </si>
+  <si>
+    <t>Roman names</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_NamePoolFrontier</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_NamePoolFrontier</t>
+  </si>
+  <si>
+    <t>Frontier names</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_NamePoolMythic</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_NamePoolMythic</t>
+  </si>
+  <si>
+    <t>Mythic names</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_NamePoolCosmic</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_NamePoolCosmic</t>
+  </si>
+  <si>
+    <t>Cosmic names</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_NamePoolRequiredMessage</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_NamePoolRequiredMessage</t>
+  </si>
+  <si>
+    <t>At least one mount name pool must remain enabled.</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_MountedJobPermissions</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_MountedJobPermissions</t>
+  </si>
+  <si>
+    <t>Mounted job permissions</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_MountedJobPermission_Tip</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_MountedJobPermission_Tip</t>
+  </si>
+  <si>
+    <t>Allows Giddy-Up to keep pawns mounted while doing this job.</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_MountedJob_RopeToPen</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_MountedJob_RopeToPen</t>
+  </si>
+  <si>
+    <t>Rope animals to pen</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_MountedJob_Strip</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_MountedJob_Strip</t>
+  </si>
+  <si>
+    <t>Strip</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_MountedJob_Dismount</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_MountedJob_Dismount</t>
+  </si>
+  <si>
+    <t>Dismount</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_MountedJob_Hunt</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_MountedJob_Hunt</t>
+  </si>
+  <si>
+    <t>Hunt</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_MountedJob_ReleasePrisoner</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_MountedJob_ReleasePrisoner</t>
+  </si>
+  <si>
+    <t>Release prisoner</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_MountedJob_EscortPrisonerToBed</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_MountedJob_EscortPrisonerToBed</t>
+  </si>
+  <si>
+    <t>Escort prisoner to bed</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_MountedJob_TakeWoundedPrisonerToBed</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_MountedJob_TakeWoundedPrisonerToBed</t>
+  </si>
+  <si>
+    <t>Take wounded prisoner to bed</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_MountedJob_Arrest</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_MountedJob_Arrest</t>
+  </si>
+  <si>
+    <t>Arrest</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_MountedJob_DeliverFood</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_MountedJob_DeliverFood</t>
+  </si>
+  <si>
+    <t>Deliver food</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_MountedJob_HaulToContainer</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_MountedJob_HaulToContainer</t>
+  </si>
+  <si>
+    <t>Deliver resources to containers/blueprints/frames</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_MountedJob_GiveToPawn</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_MountedJob_GiveToPawn</t>
+  </si>
+  <si>
+    <t>Give items to charity</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_MountedJob_EmptyThingContainer</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_MountedJob_EmptyThingContainer</t>
+  </si>
+  <si>
+    <t>Loot/open containers</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_MountedJob_SlaveEmancipation</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_MountedJob_SlaveEmancipation</t>
+  </si>
+  <si>
+    <t>Emancipate slaves</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_MountedJob_PrisonerEnslave</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_MountedJob_PrisonerEnslave</t>
+  </si>
+  <si>
+    <t>Enslave prisoner</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_MountedJob_PrisonerReduceWill</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_MountedJob_PrisonerReduceWill</t>
+  </si>
+  <si>
+    <t>Shackle/reduce prisoner will</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_MountedJob_SlaveSuppress</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_MountedJob_SlaveSuppress</t>
+  </si>
+  <si>
+    <t>Suppress slave</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Setting_MountedJob_ReleaseEntity</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Setting_MountedJob_ReleaseEntity</t>
+  </si>
+  <si>
+    <t>Release entity</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Column_AssignRider_Tip</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Column_AssignRider_Tip</t>
+  </si>
+  <si>
+    <t>Click to assign rider.
+Click and drag to copy this rider assignment to other animals.</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Column_Borrowable_Tip</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Column_Borrowable_Tip</t>
+  </si>
+  <si>
+    <t>Click to toggle borrowable.
+Click and drag to copy this setting to other animals.</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Message_AssignedRider</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Message_AssignedRider</t>
+  </si>
+  <si>
+    <t>{0} assigned to {1}</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_PreferredMate_NoValidStallions</t>
+  </si>
+  <si>
+    <t>CompanionMounts_PreferredMate_NoValidStallions</t>
+  </si>
+  <si>
+    <t>No valid stallions available</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_CaravanOwner_Tip</t>
+  </si>
+  <si>
+    <t>CompanionMounts_CaravanOwner_Tip</t>
+  </si>
+  <si>
+    <t>Mount owner: {0}</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Message_TrustLevelGained</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Message_TrustLevelGained</t>
+  </si>
+  <si>
+    <t>{0} and {1} reached trust level {2}.</t>
+  </si>
+  <si>
+    <t>Keyed+CompanionMounts_Message_MountNamed</t>
+  </si>
+  <si>
+    <t>CompanionMounts_Message_MountNamed</t>
+  </si>
+  <si>
+    <t>{0} has named {1} "{2}".</t>
+  </si>
+  <si>
+    <t>전 소유자</t>
+  </si>
+  <si>
+    <t>탈것 신뢰도: +{0}칸/초</t>
+  </si>
+  <si>
+    <t>없음</t>
+  </si>
+  <si>
+    <t>끔</t>
+  </si>
+  <si>
+    <t>초기화</t>
+  </si>
+  <si>
+    <t>선호 종마 배정 사용</t>
+  </si>
+  <si>
+    <t>활성화하면 암컷 동물에게 선호 종마를 배정할 수 있습니다. 배정된 암말은 지정된 종마와만 교미하며, 배정되지 않은 동물은 바닐라 교미 행동을 유지합니다.</t>
+  </si>
+  <si>
+    <t>선호 종마 배정을 활성화했습니다. 지원되는 동물 탭에 종마 열이 추가되었습니다.</t>
+  </si>
+  <si>
+    <t>선호 종마 배정을 비활성화했습니다. 지원되는 동물 탭에서 종마 열이 제거되었습니다.</t>
+  </si>
+  <si>
+    <t>배정된 탈것의 최소 이동 거리: {0}칸</t>
+  </si>
+  <si>
+    <t>배정된 탈것의 최대 픽업 거리: {0}칸</t>
+  </si>
+  <si>
+    <t>탈것 신뢰 시스템 사용</t>
+  </si>
+  <si>
+    <t>비활성화하면 탈것 신뢰 경험치, 신뢰 보너스, 신뢰 관련 기분 생각, 사망 기억 및 신뢰 HUD 표시가 작동하지 않습니다. 기존 신뢰 진행도는 유지됩니다.</t>
+  </si>
+  <si>
+    <t>10레벨 달성에 필요한 신뢰 경험치: {0}</t>
+  </si>
+  <si>
+    <t>신뢰도 곡선: {0}</t>
+  </si>
+  <si>
+    <t>탑승 이동 시 틱당 신뢰 경험치: {0}</t>
+  </si>
+  <si>
+    <t>쓰러진 탈것 먹이 주기 신뢰 경험치: {0}</t>
+  </si>
+  <si>
+    <t>탈것 구조 신뢰 경험치: {0}</t>
+  </si>
+  <si>
+    <t>구조 신뢰 배율: {0}배</t>
+  </si>
+  <si>
+    <t>야생성 경험치 둔화 강도: {0}</t>
+  </si>
+  <si>
+    <t>신뢰도 10레벨 탑승 시간 단축: {0}%</t>
+  </si>
+  <si>
+    <t>신뢰도 4레벨 이동 속도 보너스: +{0}칸/초</t>
+  </si>
+  <si>
+    <t>신뢰도 8레벨 이동 속도 보너스: +{0}칸/초</t>
+  </si>
+  <si>
+    <t>신뢰도 10레벨 이동 속도 보너스: +{0}칸/초</t>
+  </si>
+  <si>
+    <t>RimHUD에 탈것 소유권 행 자동 추가</t>
+  </si>
+  <si>
+    <t>비활성화하면 탈것 소유권의 RimHUD 값은 수동 배치용으로 계속 사용할 수 있으며, 다른 모드가 선호하는 HUD 위치에 강제로 배치되지 않습니다.</t>
+  </si>
+  <si>
+    <t>탈것 이름 목록</t>
+  </si>
+  <si>
+    <t>간단한 이름</t>
+  </si>
+  <si>
+    <t>중세풍 이름</t>
+  </si>
+  <si>
+    <t>로마풍 이름</t>
+  </si>
+  <si>
+    <t>개척지풍 이름</t>
+  </si>
+  <si>
+    <t>신화풍 이름</t>
+  </si>
+  <si>
+    <t>우주풍 이름</t>
+  </si>
+  <si>
+    <t>탈것 이름 목록을 하나 이상 활성화해야 합니다.</t>
+  </si>
+  <si>
+    <t>탑승 중 작업 허용 설정</t>
+  </si>
+  <si>
+    <t>이 작업을 하는 동안 Giddy-Up이 정착민을 탑승 상태로 유지하도록 허용합니다.</t>
+  </si>
+  <si>
+    <t>동물을 우리로 끌고 가기</t>
+  </si>
+  <si>
+    <t>옷 벗기기</t>
+  </si>
+  <si>
+    <t>하차</t>
+  </si>
+  <si>
+    <t>사냥</t>
+  </si>
+  <si>
+    <t>죄수 석방</t>
+  </si>
+  <si>
+    <t>죄수를 침대로 호송</t>
+  </si>
+  <si>
+    <t>부상당한 죄수를 침대로 운반</t>
+  </si>
+  <si>
+    <t>체포</t>
+  </si>
+  <si>
+    <t>음식 배달</t>
+  </si>
+  <si>
+    <t>자원을 보관함/청사진/건설틀로 운반</t>
+  </si>
+  <si>
+    <t>노예 해방</t>
+  </si>
+  <si>
+    <t>죄수를 노예로 만들기</t>
+  </si>
+  <si>
+    <t>죄수에게 족쇄 채우기/의지 감소</t>
+  </si>
+  <si>
+    <t>노예 억압</t>
+  </si>
+  <si>
+    <t>개체 방출</t>
+  </si>
+  <si>
+    <t>클릭하여 기승자를 배정합니다.
+클릭한 채 드래그하면 이 기승자 배정을 다른 동물에게 복사합니다.</t>
+  </si>
+  <si>
+    <t>클릭하여 대여 가능 여부를 전환합니다.
+클릭한 채 드래그하면 이 설정을 다른 동물에게 복사합니다.</t>
+  </si>
+  <si>
+    <t>배정 가능한 유효한 종마가 없습니다.</t>
+  </si>
+  <si>
+    <t>탈것 소유자: {0}</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탈것이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>여러</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>마리라서</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기분이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>좋아</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>여가 승마 신뢰 배율: {0}배</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>상자 약탈/열기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}(을)를 {1}에게 배정했습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}(와)과 {1}의 신뢰도가 {2}레벨에 도달했습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}(이)가 {1}에게 "{2}"(이)라는 이름을 지어 주었습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>- Mount Ownership -</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>물품 기부</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -929,7 +1767,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -945,6 +1783,19 @@
     <font>
       <sz val="8"/>
       <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -972,11 +1823,9 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -995,7 +1844,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1037,9 +1886,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1052,12 +1901,52 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="dk1"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="accent1"/>
-        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525">
@@ -1115,7 +2004,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1141,7 +2030,7 @@
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1170,20 +2059,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="51.5703125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="61.85546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="61.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="37" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19" style="1" customWidth="1"/>
+    <col min="5" max="5" width="61.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="80.28515625" style="1" customWidth="1"/>
     <col min="7" max="7" width="9.140625" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1199,14 +2088,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -1219,1538 +2105,2592 @@
       <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>31</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>289</v>
+        <v>62</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>254</v>
+        <v>47</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>290</v>
+        <v>68</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>255</v>
+        <v>73</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>256</v>
+        <v>78</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>257</v>
+        <v>82</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>291</v>
+        <v>86</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>257</v>
+        <v>82</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>292</v>
+        <v>92</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>258</v>
+        <v>96</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>293</v>
+        <v>100</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>258</v>
+        <v>96</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>293</v>
+        <v>100</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>258</v>
+        <v>96</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>293</v>
+        <v>100</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>258</v>
+        <v>96</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>293</v>
+        <v>100</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>258</v>
+        <v>96</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>293</v>
+        <v>100</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>258</v>
+        <v>96</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C36" s="1" t="s">
+      <c r="F36" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>258</v>
+        <v>96</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>293</v>
+        <v>100</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>258</v>
+        <v>96</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>293</v>
+        <v>100</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>258</v>
+        <v>96</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>293</v>
+        <v>100</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>258</v>
+        <v>96</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>293</v>
+        <v>100</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>259</v>
+        <v>140</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>294</v>
+        <v>144</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>259</v>
+        <v>140</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>294</v>
+        <v>144</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>259</v>
+        <v>140</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>294</v>
+        <v>144</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>259</v>
+        <v>140</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>294</v>
+        <v>144</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>259</v>
+        <v>140</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>294</v>
+        <v>144</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="1" t="s">
+      <c r="F55" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>294</v>
+        <v>144</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>259</v>
+        <v>140</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>294</v>
+        <v>144</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>259</v>
+        <v>140</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>294</v>
+        <v>144</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>259</v>
+        <v>140</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>294</v>
+        <v>144</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>259</v>
+        <v>140</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>294</v>
+        <v>144</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>260</v>
+        <v>185</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>164</v>
+        <v>187</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>261</v>
+        <v>189</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>167</v>
+        <v>191</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>262</v>
+        <v>194</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>263</v>
+        <v>198</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>262</v>
+        <v>194</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>264</v>
+        <v>204</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>265</v>
+        <v>208</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>266</v>
+        <v>212</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>186</v>
+        <v>215</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>267</v>
+        <v>216</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>188</v>
+        <v>218</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>189</v>
+        <v>219</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>268</v>
+        <v>220</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>191</v>
+        <v>222</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>193</v>
+        <v>224</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>269</v>
+        <v>225</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>270</v>
+        <v>229</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>192</v>
+        <v>223</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>199</v>
+        <v>232</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>271</v>
+        <v>233</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>201</v>
+        <v>235</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>203</v>
+        <v>237</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>269</v>
+        <v>225</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>204</v>
+        <v>238</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>205</v>
+        <v>239</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>272</v>
+        <v>240</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>207</v>
+        <v>242</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>208</v>
+        <v>243</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>273</v>
+        <v>244</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>210</v>
+        <v>246</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>274</v>
+        <v>248</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>213</v>
+        <v>250</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>214</v>
+        <v>251</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>275</v>
+        <v>252</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>216</v>
+        <v>254</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>217</v>
+        <v>255</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>276</v>
+        <v>256</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>219</v>
+        <v>258</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>220</v>
+        <v>259</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>277</v>
+        <v>260</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>222</v>
+        <v>262</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>223</v>
+        <v>263</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>278</v>
+        <v>264</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>225</v>
+        <v>266</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>226</v>
+        <v>267</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>279</v>
+        <v>268</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>228</v>
+        <v>270</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>280</v>
+        <v>272</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>231</v>
+        <v>274</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>234</v>
+        <v>278</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>235</v>
+        <v>279</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>237</v>
+        <v>282</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>238</v>
+        <v>283</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>239</v>
+        <v>284</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>240</v>
+        <v>285</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>241</v>
+        <v>286</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>295</v>
+        <v>287</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>243</v>
+        <v>289</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>202</v>
+        <v>236</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>244</v>
+        <v>290</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>284</v>
+        <v>291</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A132" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>540</v>
       </c>
     </row>
   </sheetData>
